--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a1.00_b1.00_x0.10_Q80_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a1.00_b1.00_x0.10_Q80_LO.xlsx
@@ -455,10 +455,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0107750442929737</v>
+        <v>0.009607539667423377</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0107750442929737</v>
+        <v>0.009607539667423377</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -469,10 +469,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.01687093267012585</v>
+        <v>0.01537002462715287</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01687093267012585</v>
+        <v>0.01537002462715287</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -483,10 +483,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03194125781963783</v>
+        <v>0.02910341524119371</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03194125781963783</v>
+        <v>0.02910341524119371</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -497,10 +497,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.05152362404729748</v>
+        <v>0.04686417538385653</v>
       </c>
       <c r="C5" t="n">
-        <v>0.05152362404729748</v>
+        <v>0.04686417538385653</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -511,10 +511,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.06777483666026715</v>
+        <v>0.06177418768643925</v>
       </c>
       <c r="C6" t="n">
-        <v>0.06777483666026715</v>
+        <v>0.06177418768643925</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -525,10 +525,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.07326699568678768</v>
+        <v>0.06673731457035675</v>
       </c>
       <c r="C7" t="n">
-        <v>0.07326699568678768</v>
+        <v>0.06673731457035675</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -539,10 +539,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.07146508036946485</v>
+        <v>0.0650735275676106</v>
       </c>
       <c r="C8" t="n">
-        <v>0.07146508036946485</v>
+        <v>0.0650735275676106</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -553,10 +553,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.06716222834032871</v>
+        <v>0.0611893776347822</v>
       </c>
       <c r="C9" t="n">
-        <v>0.06716222834032871</v>
+        <v>0.0611893776347822</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -567,10 +567,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0626512315303502</v>
+        <v>0.05703876412569865</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0626512315303502</v>
+        <v>0.05703876412569865</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -581,10 +581,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.06050670960061443</v>
+        <v>0.05356458127995362</v>
       </c>
       <c r="C11" t="n">
-        <v>0.06050670960061443</v>
+        <v>0.05356458127995362</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
